--- a/Comparison.xlsx
+++ b/Comparison.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\NIKOO BHI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nikoo\Documents\GitHub\Emognition-Processing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3101E7D9-FB55-4677-9697-42493467CBBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22CC0A77-ADA3-4332-8756-C014DAD3E87A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="26640" windowHeight="14490" activeTab="1" xr2:uid="{A5FF6E23-3576-4FDC-B007-30627E43C8F7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{A5FF6E23-3576-4FDC-B007-30627E43C8F7}"/>
   </bookViews>
   <sheets>
     <sheet name="DATA" sheetId="1" r:id="rId1"/>
@@ -37,9 +37,6 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1083,7 +1080,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1091,7 +1088,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1110,7 +1106,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1135,6 +1131,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1157,9 +1156,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1238,7 +1234,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropLines="10" dropStyle="combo" dx="22" fmlaLink="$C$10" fmlaRange="$CI$2:$CI$7" noThreeD="1" sel="2" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropLines="10" dropStyle="combo" dx="22" fmlaLink="$C$10" fmlaRange="$CI$2:$CI$7" noThreeD="1" sel="6" val="0"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1248,15 +1244,15 @@
       <xdr:twoCellAnchor editAs="absolute">
         <xdr:from>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>1</xdr:row>
-          <xdr:rowOff>9525</xdr:rowOff>
+          <xdr:rowOff>7620</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>6</xdr:col>
-          <xdr:colOff>28575</xdr:colOff>
+          <xdr:colOff>30480</xdr:colOff>
           <xdr:row>1</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1306,15 +1302,15 @@
       <xdr:twoCellAnchor editAs="absolute">
         <xdr:from>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>9525</xdr:colOff>
+          <xdr:colOff>7620</xdr:colOff>
           <xdr:row>3</xdr:row>
-          <xdr:rowOff>9525</xdr:rowOff>
+          <xdr:rowOff>7620</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>6</xdr:col>
-          <xdr:colOff>28575</xdr:colOff>
+          <xdr:colOff>30480</xdr:colOff>
           <xdr:row>3</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1364,15 +1360,15 @@
       <xdr:twoCellAnchor editAs="absolute">
         <xdr:from>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>5</xdr:row>
-          <xdr:rowOff>9525</xdr:rowOff>
+          <xdr:rowOff>7620</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>6</xdr:col>
           <xdr:colOff>38100</xdr:colOff>
           <xdr:row>5</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1422,15 +1418,15 @@
       <xdr:twoCellAnchor editAs="absolute">
         <xdr:from>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>7</xdr:row>
-          <xdr:rowOff>9525</xdr:rowOff>
+          <xdr:rowOff>7620</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>6</xdr:col>
           <xdr:colOff>38100</xdr:colOff>
           <xdr:row>7</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1480,15 +1476,15 @@
       <xdr:twoCellAnchor editAs="absolute">
         <xdr:from>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>19050</xdr:colOff>
+          <xdr:colOff>22860</xdr:colOff>
           <xdr:row>9</xdr:row>
-          <xdr:rowOff>9525</xdr:rowOff>
+          <xdr:rowOff>7620</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>6</xdr:col>
           <xdr:colOff>38100</xdr:colOff>
           <xdr:row>9</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
+          <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1854,9 +1850,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8121070E-B702-4F8C-BFEE-B3EDE451ACAF}">
   <dimension ref="A1:AZ118"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2014,7 +2010,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>52</v>
       </c>
@@ -2172,7 +2168,7 @@
         <v>0.61631313648099995</v>
       </c>
     </row>
-    <row r="3" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -2330,7 +2326,7 @@
         <v>0.638080902522</v>
       </c>
     </row>
-    <row r="4" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>60</v>
       </c>
@@ -2488,7 +2484,7 @@
         <v>0.59077655220799996</v>
       </c>
     </row>
-    <row r="5" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>62</v>
       </c>
@@ -2646,7 +2642,7 @@
         <v>0.64027998568900002</v>
       </c>
     </row>
-    <row r="6" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -2804,7 +2800,7 @@
         <v>0.62758300922700005</v>
       </c>
     </row>
-    <row r="7" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>66</v>
       </c>
@@ -2962,7 +2958,7 @@
         <v>0.64975066272600002</v>
       </c>
     </row>
-    <row r="8" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>67</v>
       </c>
@@ -3120,7 +3116,7 @@
         <v>0.59979455035100004</v>
       </c>
     </row>
-    <row r="9" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>68</v>
       </c>
@@ -3278,7 +3274,7 @@
         <v>0.63962920030399995</v>
       </c>
     </row>
-    <row r="10" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>69</v>
       </c>
@@ -3436,7 +3432,7 @@
         <v>0.57324990728199998</v>
       </c>
     </row>
-    <row r="11" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>71</v>
       </c>
@@ -3594,7 +3590,7 @@
         <v>0.60057956608899998</v>
       </c>
     </row>
-    <row r="12" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>72</v>
       </c>
@@ -3752,7 +3748,7 @@
         <v>0.55985259441000002</v>
       </c>
     </row>
-    <row r="13" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>73</v>
       </c>
@@ -3910,7 +3906,7 @@
         <v>0.63195879051000003</v>
       </c>
     </row>
-    <row r="14" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>74</v>
       </c>
@@ -4068,7 +4064,7 @@
         <v>0.64041681233900005</v>
       </c>
     </row>
-    <row r="15" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>76</v>
       </c>
@@ -4226,7 +4222,7 @@
         <v>0.63204781382099995</v>
       </c>
     </row>
-    <row r="16" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>77</v>
       </c>
@@ -4384,7 +4380,7 @@
         <v>0.61389570066400001</v>
       </c>
     </row>
-    <row r="17" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>78</v>
       </c>
@@ -4542,7 +4538,7 @@
         <v>0.63517776249400004</v>
       </c>
     </row>
-    <row r="18" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>79</v>
       </c>
@@ -4700,7 +4696,7 @@
         <v>0.60062275271800003</v>
       </c>
     </row>
-    <row r="19" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>81</v>
       </c>
@@ -4858,7 +4854,7 @@
         <v>0.59967705075099997</v>
       </c>
     </row>
-    <row r="20" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>82</v>
       </c>
@@ -5016,7 +5012,7 @@
         <v>0.57251356814400001</v>
       </c>
     </row>
-    <row r="21" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>83</v>
       </c>
@@ -5174,7 +5170,7 @@
         <v>0.60245309227999999</v>
       </c>
     </row>
-    <row r="22" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>84</v>
       </c>
@@ -5332,7 +5328,7 @@
         <v>0.62403081820200001</v>
       </c>
     </row>
-    <row r="23" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>86</v>
       </c>
@@ -5490,7 +5486,7 @@
         <v>0.65571731870299999</v>
       </c>
     </row>
-    <row r="24" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>87</v>
       </c>
@@ -5648,7 +5644,7 @@
         <v>0.61140869465500003</v>
       </c>
     </row>
-    <row r="25" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>88</v>
       </c>
@@ -5806,7 +5802,7 @@
         <v>0.69221040227099995</v>
       </c>
     </row>
-    <row r="26" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>89</v>
       </c>
@@ -5964,7 +5960,7 @@
         <v>0.65588766044900004</v>
       </c>
     </row>
-    <row r="27" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>90</v>
       </c>
@@ -6122,7 +6118,7 @@
         <v>0.72504647875399997</v>
       </c>
     </row>
-    <row r="28" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>91</v>
       </c>
@@ -6280,7 +6276,7 @@
         <v>0.65158869411599996</v>
       </c>
     </row>
-    <row r="29" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>92</v>
       </c>
@@ -6438,7 +6434,7 @@
         <v>0.71639411872299996</v>
       </c>
     </row>
-    <row r="30" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>93</v>
       </c>
@@ -6596,7 +6592,7 @@
         <v>0.63719221703600004</v>
       </c>
     </row>
-    <row r="31" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>94</v>
       </c>
@@ -6754,7 +6750,7 @@
         <v>0.67178870719200001</v>
       </c>
     </row>
-    <row r="32" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>95</v>
       </c>
@@ -6912,7 +6908,7 @@
         <v>0.58933186444700003</v>
       </c>
     </row>
-    <row r="33" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>96</v>
       </c>
@@ -7070,7 +7066,7 @@
         <v>0.65572926952199995</v>
       </c>
     </row>
-    <row r="34" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>97</v>
       </c>
@@ -7228,7 +7224,7 @@
         <v>0.65934422708700002</v>
       </c>
     </row>
-    <row r="35" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>98</v>
       </c>
@@ -7386,7 +7382,7 @@
         <v>0.71701782398900005</v>
       </c>
     </row>
-    <row r="36" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>99</v>
       </c>
@@ -7544,7 +7540,7 @@
         <v>0.628600029723</v>
       </c>
     </row>
-    <row r="37" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>100</v>
       </c>
@@ -7702,7 +7698,7 @@
         <v>0.72683546184699999</v>
       </c>
     </row>
-    <row r="38" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>101</v>
       </c>
@@ -7860,7 +7856,7 @@
         <v>0.59839706583499996</v>
       </c>
     </row>
-    <row r="39" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>102</v>
       </c>
@@ -8018,7 +8014,7 @@
         <v>0.65342725487599995</v>
       </c>
     </row>
-    <row r="40" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>103</v>
       </c>
@@ -8176,7 +8172,7 @@
         <v>0.60787767441700002</v>
       </c>
     </row>
-    <row r="41" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>104</v>
       </c>
@@ -8334,7 +8330,7 @@
         <v>0.652644306487</v>
       </c>
     </row>
-    <row r="42" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>105</v>
       </c>
@@ -8492,7 +8488,7 @@
         <v>0.56478882851900003</v>
       </c>
     </row>
-    <row r="43" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>107</v>
       </c>
@@ -8650,7 +8646,7 @@
         <v>0.66070987047499996</v>
       </c>
     </row>
-    <row r="44" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>108</v>
       </c>
@@ -8808,7 +8804,7 @@
         <v>0.53743082280599996</v>
       </c>
     </row>
-    <row r="45" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>109</v>
       </c>
@@ -8966,7 +8962,7 @@
         <v>0.691920841796</v>
       </c>
     </row>
-    <row r="46" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>110</v>
       </c>
@@ -9124,7 +9120,7 @@
         <v>0.63367452308799999</v>
       </c>
     </row>
-    <row r="47" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>111</v>
       </c>
@@ -9282,7 +9278,7 @@
         <v>0.65804976900300005</v>
       </c>
     </row>
-    <row r="48" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>112</v>
       </c>
@@ -9440,7 +9436,7 @@
         <v>0.59961447652800004</v>
       </c>
     </row>
-    <row r="49" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>113</v>
       </c>
@@ -9598,7 +9594,7 @@
         <v>0.64274606496200004</v>
       </c>
     </row>
-    <row r="50" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>114</v>
       </c>
@@ -9756,7 +9752,7 @@
         <v>0.61351050652500005</v>
       </c>
     </row>
-    <row r="51" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>115</v>
       </c>
@@ -9914,7 +9910,7 @@
         <v>0.57063801921000001</v>
       </c>
     </row>
-    <row r="52" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>116</v>
       </c>
@@ -10072,7 +10068,7 @@
         <v>0.62414986626199997</v>
       </c>
     </row>
-    <row r="53" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>117</v>
       </c>
@@ -10230,7 +10226,7 @@
         <v>0.60197834689100005</v>
       </c>
     </row>
-    <row r="54" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>118</v>
       </c>
@@ -10388,7 +10384,7 @@
         <v>0.58031831878100004</v>
       </c>
     </row>
-    <row r="55" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>119</v>
       </c>
@@ -10546,7 +10542,7 @@
         <v>0.64232392758699997</v>
       </c>
     </row>
-    <row r="56" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>120</v>
       </c>
@@ -10704,7 +10700,7 @@
         <v>0.60964286486999997</v>
       </c>
     </row>
-    <row r="57" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>121</v>
       </c>
@@ -10862,7 +10858,7 @@
         <v>0.70051778286099997</v>
       </c>
     </row>
-    <row r="58" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>122</v>
       </c>
@@ -11020,7 +11016,7 @@
         <v>0.62515688846799999</v>
       </c>
     </row>
-    <row r="59" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>123</v>
       </c>
@@ -11178,7 +11174,7 @@
         <v>0.62752754512599995</v>
       </c>
     </row>
-    <row r="60" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>124</v>
       </c>
@@ -11336,7 +11332,7 @@
         <v>0.57839417253000003</v>
       </c>
     </row>
-    <row r="61" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>125</v>
       </c>
@@ -11494,7 +11490,7 @@
         <v>0.67979680564900002</v>
       </c>
     </row>
-    <row r="62" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>126</v>
       </c>
@@ -11652,7 +11648,7 @@
         <v>0.52234695332900005</v>
       </c>
     </row>
-    <row r="63" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>127</v>
       </c>
@@ -11810,7 +11806,7 @@
         <v>0.56433885845800003</v>
       </c>
     </row>
-    <row r="64" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>128</v>
       </c>
@@ -11968,7 +11964,7 @@
         <v>0.56111706711200005</v>
       </c>
     </row>
-    <row r="65" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>129</v>
       </c>
@@ -12126,7 +12122,7 @@
         <v>0.60561607716200005</v>
       </c>
     </row>
-    <row r="66" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>130</v>
       </c>
@@ -12284,7 +12280,7 @@
         <v>0.63703239176899995</v>
       </c>
     </row>
-    <row r="67" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>131</v>
       </c>
@@ -12442,7 +12438,7 @@
         <v>0.63638617825400001</v>
       </c>
     </row>
-    <row r="68" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>132</v>
       </c>
@@ -12600,7 +12596,7 @@
         <v>0.61829354845999995</v>
       </c>
     </row>
-    <row r="69" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>133</v>
       </c>
@@ -12758,7 +12754,7 @@
         <v>0.61629028736699998</v>
       </c>
     </row>
-    <row r="70" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>134</v>
       </c>
@@ -12916,7 +12912,7 @@
         <v>0.55491290562999995</v>
       </c>
     </row>
-    <row r="71" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>135</v>
       </c>
@@ -13074,7 +13070,7 @@
         <v>0.57511271439099998</v>
       </c>
     </row>
-    <row r="72" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>136</v>
       </c>
@@ -13232,7 +13228,7 @@
         <v>0.57362034055300004</v>
       </c>
     </row>
-    <row r="73" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>137</v>
       </c>
@@ -13390,7 +13386,7 @@
         <v>0.58877761622699998</v>
       </c>
     </row>
-    <row r="74" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>138</v>
       </c>
@@ -13548,7 +13544,7 @@
         <v>0.53733398415300004</v>
       </c>
     </row>
-    <row r="75" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>139</v>
       </c>
@@ -13706,7 +13702,7 @@
         <v>0.60371158435299999</v>
       </c>
     </row>
-    <row r="76" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>140</v>
       </c>
@@ -13864,7 +13860,7 @@
         <v>0.61119900150899997</v>
       </c>
     </row>
-    <row r="77" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>141</v>
       </c>
@@ -14022,7 +14018,7 @@
         <v>0.60223647759499999</v>
       </c>
     </row>
-    <row r="78" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>142</v>
       </c>
@@ -14180,7 +14176,7 @@
         <v>0.47342439567099998</v>
       </c>
     </row>
-    <row r="79" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>143</v>
       </c>
@@ -14338,7 +14334,7 @@
         <v>0.57490824986900002</v>
       </c>
     </row>
-    <row r="80" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>144</v>
       </c>
@@ -14496,7 +14492,7 @@
         <v>0.559110542712</v>
       </c>
     </row>
-    <row r="81" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>145</v>
       </c>
@@ -14654,7 +14650,7 @@
         <v>0.59857411094699997</v>
       </c>
     </row>
-    <row r="82" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>180</v>
       </c>
@@ -14812,7 +14808,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="83" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>183</v>
       </c>
@@ -14970,7 +14966,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="84" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>184</v>
       </c>
@@ -15128,7 +15124,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="85" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>185</v>
       </c>
@@ -15286,7 +15282,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="86" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>186</v>
       </c>
@@ -15444,7 +15440,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="87" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>187</v>
       </c>
@@ -15602,7 +15598,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="88" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>188</v>
       </c>
@@ -15760,7 +15756,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="89" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>189</v>
       </c>
@@ -15918,7 +15914,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="90" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>190</v>
       </c>
@@ -16076,7 +16072,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="91" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>191</v>
       </c>
@@ -16234,7 +16230,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="92" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>192</v>
       </c>
@@ -16392,7 +16388,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="93" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>193</v>
       </c>
@@ -16550,7 +16546,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="94" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>194</v>
       </c>
@@ -16708,7 +16704,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="95" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>195</v>
       </c>
@@ -16866,7 +16862,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="96" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>196</v>
       </c>
@@ -17024,7 +17020,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="97" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>197</v>
       </c>
@@ -17182,7 +17178,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="98" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>198</v>
       </c>
@@ -17340,7 +17336,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="99" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>199</v>
       </c>
@@ -17498,7 +17494,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="100" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>200</v>
       </c>
@@ -17656,7 +17652,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="101" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>201</v>
       </c>
@@ -17814,7 +17810,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="102" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>0</v>
       </c>
@@ -17972,7 +17968,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="103" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>202</v>
       </c>
@@ -18130,7 +18126,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="104" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>209</v>
       </c>
@@ -18288,7 +18284,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="105" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>204</v>
       </c>
@@ -18446,7 +18442,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="106" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>210</v>
       </c>
@@ -18604,7 +18600,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="107" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>214</v>
       </c>
@@ -18762,7 +18758,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="108" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>213</v>
       </c>
@@ -18920,7 +18916,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="109" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>215</v>
       </c>
@@ -19078,7 +19074,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="110" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>208</v>
       </c>
@@ -19236,7 +19232,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="111" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>219</v>
       </c>
@@ -19394,7 +19390,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="112" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>217</v>
       </c>
@@ -19552,7 +19548,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="113" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>212</v>
       </c>
@@ -19710,7 +19706,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="114" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>207</v>
       </c>
@@ -19868,7 +19864,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="115" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>216</v>
       </c>
@@ -20026,7 +20022,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="116" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>206</v>
       </c>
@@ -20184,7 +20180,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="117" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>211</v>
       </c>
@@ -20342,7 +20338,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="118" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>218</v>
       </c>
@@ -20508,62 +20504,62 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E0DCF50-CB17-4CBD-89F5-BEAA62AA47EA}">
   <dimension ref="B1:CI20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5703125" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="9.140625" customWidth="1"/>
-    <col min="12" max="12" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="9.140625" customWidth="1"/>
-    <col min="14" max="14" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="9.140625" customWidth="1"/>
-    <col min="16" max="16" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="9.140625" customWidth="1"/>
-    <col min="18" max="18" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="9.140625" customWidth="1"/>
-    <col min="20" max="20" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="9.140625" customWidth="1"/>
-    <col min="22" max="22" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="23" max="23" width="9.140625" customWidth="1"/>
-    <col min="24" max="24" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="25" max="25" width="9.140625" customWidth="1"/>
-    <col min="26" max="26" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="27" max="27" width="9.140625" customWidth="1"/>
-    <col min="28" max="28" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="29" max="29" width="9.140625" customWidth="1"/>
-    <col min="30" max="30" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="31" max="31" width="9.140625" customWidth="1"/>
-    <col min="32" max="32" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="33" max="33" width="9.140625" customWidth="1"/>
-    <col min="34" max="34" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" customWidth="1"/>
-    <col min="36" max="36" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="37" max="37" width="9.140625" customWidth="1"/>
-    <col min="38" max="38" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="39" max="39" width="9.140625" customWidth="1"/>
-    <col min="40" max="40" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="41" max="41" width="9.140625" customWidth="1"/>
-    <col min="42" max="42" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="9.140625" customWidth="1"/>
-    <col min="44" max="44" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="45" max="45" width="9.140625" customWidth="1"/>
-    <col min="46" max="46" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="47" max="47" width="9.140625" customWidth="1"/>
-    <col min="48" max="48" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="49" max="49" width="9.140625" customWidth="1"/>
-    <col min="50" max="50" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="51" max="51" width="9.140625" customWidth="1"/>
-    <col min="52" max="52" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="53" max="53" width="9.140625" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5546875" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="9.109375" customWidth="1"/>
+    <col min="8" max="8" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="9.109375" customWidth="1"/>
+    <col min="10" max="10" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="9.109375" customWidth="1"/>
+    <col min="12" max="12" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="9.109375" customWidth="1"/>
+    <col min="14" max="14" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="9.109375" customWidth="1"/>
+    <col min="16" max="16" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="9.109375" customWidth="1"/>
+    <col min="18" max="18" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="9.109375" customWidth="1"/>
+    <col min="20" max="20" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="9.109375" customWidth="1"/>
+    <col min="22" max="22" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="9.109375" customWidth="1"/>
+    <col min="24" max="24" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="25" max="25" width="9.109375" customWidth="1"/>
+    <col min="26" max="26" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="27" max="27" width="9.109375" customWidth="1"/>
+    <col min="28" max="28" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="29" max="29" width="9.109375" customWidth="1"/>
+    <col min="30" max="30" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="31" max="31" width="9.109375" customWidth="1"/>
+    <col min="32" max="32" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="33" max="33" width="9.109375" customWidth="1"/>
+    <col min="34" max="34" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="35" max="35" width="9.109375" customWidth="1"/>
+    <col min="36" max="36" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="37" max="37" width="9.109375" customWidth="1"/>
+    <col min="38" max="38" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="39" max="39" width="9.109375" customWidth="1"/>
+    <col min="40" max="40" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="41" max="41" width="9.109375" customWidth="1"/>
+    <col min="42" max="42" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="43" max="43" width="9.109375" customWidth="1"/>
+    <col min="44" max="44" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="45" max="45" width="9.109375" customWidth="1"/>
+    <col min="46" max="46" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="47" max="47" width="9.109375" customWidth="1"/>
+    <col min="48" max="48" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="49" max="49" width="9.109375" customWidth="1"/>
+    <col min="50" max="50" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="51" max="51" width="9.109375" customWidth="1"/>
+    <col min="52" max="52" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="53" max="53" width="9.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:87" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:87" x14ac:dyDescent="0.3">
       <c r="BZ1" t="s">
         <v>174</v>
       </c>
@@ -20595,7 +20591,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="2" spans="2:87" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:87" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>146</v>
       </c>
@@ -20637,7 +20633,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="3" spans="2:87" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:87" x14ac:dyDescent="0.3">
       <c r="B3" s="2"/>
       <c r="BZ3">
         <v>2</v>
@@ -20670,7 +20666,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="2:87" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:87" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
         <v>147</v>
       </c>
@@ -20694,7 +20690,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="5" spans="2:87" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:87" x14ac:dyDescent="0.3">
       <c r="B5" s="2"/>
       <c r="BZ5">
         <v>4</v>
@@ -20709,7 +20705,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="6" spans="2:87" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:87" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
         <v>175</v>
       </c>
@@ -20733,7 +20729,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="7" spans="2:87" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:87" x14ac:dyDescent="0.3">
       <c r="BZ7">
         <v>6</v>
       </c>
@@ -20747,7 +20743,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="8" spans="2:87" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:87" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>222</v>
       </c>
@@ -20761,7 +20757,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="9" spans="2:87" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:87" x14ac:dyDescent="0.3">
       <c r="B9" s="1"/>
       <c r="BZ9">
         <v>8</v>
@@ -20770,12 +20766,12 @@
         <v>167</v>
       </c>
     </row>
-    <row r="10" spans="2:87" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:87" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>223</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BZ10">
         <v>9</v>
@@ -20784,23 +20780,12 @@
         <v>168</v>
       </c>
     </row>
-    <row r="11" spans="2:87" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
+    <row r="11" spans="2:87" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
     </row>
-    <row r="12" spans="2:87" s="4" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:87" s="3" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="19" t="s">
         <v>179</v>
       </c>
@@ -20867,1590 +20852,1590 @@
       <c r="BA12"/>
       <c r="BB12"/>
     </row>
-    <row r="13" spans="2:87" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:87" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="20"/>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="G13" s="13" t="s">
+      <c r="G13" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="H13" s="13" t="s">
+      <c r="H13" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="I13" s="13" t="s">
+      <c r="I13" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="J13" s="13" t="s">
+      <c r="J13" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="K13" s="13" t="s">
+      <c r="K13" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="L13" s="14" t="s">
+      <c r="L13" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="M13" s="12" t="s">
+      <c r="M13" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="N13" s="13" t="s">
+      <c r="N13" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="O13" s="13" t="s">
+      <c r="O13" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="P13" s="13" t="s">
+      <c r="P13" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="Q13" s="13" t="s">
+      <c r="Q13" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="R13" s="13" t="s">
+      <c r="R13" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="S13" s="13" t="s">
+      <c r="S13" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="T13" s="13" t="s">
+      <c r="T13" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="U13" s="13" t="s">
+      <c r="U13" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="V13" s="14" t="s">
+      <c r="V13" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="W13" s="12" t="s">
+      <c r="W13" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="X13" s="13" t="s">
+      <c r="X13" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="Y13" s="13" t="s">
+      <c r="Y13" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="Z13" s="13" t="s">
+      <c r="Z13" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="AA13" s="13" t="s">
+      <c r="AA13" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="AB13" s="13" t="s">
+      <c r="AB13" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="AC13" s="13" t="s">
+      <c r="AC13" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="AD13" s="13" t="s">
+      <c r="AD13" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="AE13" s="13" t="s">
+      <c r="AE13" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="AF13" s="14" t="s">
+      <c r="AF13" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="AG13" s="12" t="s">
+      <c r="AG13" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="AH13" s="13" t="s">
+      <c r="AH13" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="AI13" s="13" t="s">
+      <c r="AI13" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="AJ13" s="13" t="s">
+      <c r="AJ13" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="AK13" s="13" t="s">
+      <c r="AK13" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="AL13" s="13" t="s">
+      <c r="AL13" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="AM13" s="13" t="s">
+      <c r="AM13" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="AN13" s="13" t="s">
+      <c r="AN13" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="AO13" s="13" t="s">
+      <c r="AO13" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="AP13" s="14" t="s">
+      <c r="AP13" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="AQ13" s="15" t="s">
+      <c r="AQ13" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="AR13" s="16" t="s">
+      <c r="AR13" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="AS13" s="16" t="s">
+      <c r="AS13" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="AT13" s="16" t="s">
+      <c r="AT13" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="AU13" s="16" t="s">
+      <c r="AU13" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="AV13" s="16" t="s">
+      <c r="AV13" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="AW13" s="16" t="s">
+      <c r="AW13" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="AX13" s="16" t="s">
+      <c r="AX13" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="AY13" s="17" t="s">
+      <c r="AY13" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="AZ13" s="10"/>
+      <c r="AZ13" s="9"/>
     </row>
-    <row r="14" spans="2:87" x14ac:dyDescent="0.25">
-      <c r="B14" s="11" t="s">
+    <row r="14" spans="2:87" x14ac:dyDescent="0.3">
+      <c r="B14" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="4">
         <f>IF(SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12))=0,"-",SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12)))</f>
         <v>0.46402877697799999</v>
       </c>
-      <c r="D14" s="6" t="b">
+      <c r="D14" s="5" t="b">
         <f t="shared" ref="D14:D20" si="0">IF($C$8=1,AND(MAX($C14,$M14,$W14,$AG14,$AQ14)=C14,C14&lt;&gt;0),AND(MAX($C$14:$C$20,$M$14:$M$20,$W$14:$W$20,$AG$14:$AG$20,$AQ$14:$AQ$20)=C14,C14&lt;&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="5">
         <f>IF(SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12))=0,"-",SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12)))</f>
         <v>0.45405955050300001</v>
       </c>
-      <c r="F14" s="6" t="b">
+      <c r="F14" s="5" t="b">
         <f t="shared" ref="F14:F20" si="1">IF($C$8=1,AND(MAX($E14,$O14,$Y14,$AI14,$AS14)=E14,E14&lt;&gt;0),AND(MAX($E$14:$E$20,$O$14:$O$20,$Y$14:$Y$20,$AI$14:$AI$20,$AS$14:$AS$14)=E14,E14&lt;&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="5">
         <f>IF(SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12))=0,"-",SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12)))</f>
         <v>0.45201525054500002</v>
       </c>
-      <c r="H14" s="6" t="b">
+      <c r="H14" s="5" t="b">
         <f t="shared" ref="H14:H20" si="2">IF($C$8=1,AND(MAX($G14,$Q14,$AA14,$AK14,$AU14)=G14,G14&lt;&gt;0),AND(MAX($G$14:$G$20,$Q$14:$Q$20,$AA$14:$AA$20,$AK$14:$AK$20,$AU$14:$AU$20)=G14,G14&lt;&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="I14" s="6">
+      <c r="I14" s="5">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12)))</f>
         <v>0.45405955050300001</v>
       </c>
-      <c r="J14" s="6" t="str">
+      <c r="J14" s="5" t="str">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(D$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(D$12)))</f>
         <v>-</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="5">
         <f>IF(SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12))=0,"-",SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12)))</f>
         <v>0.45089149599</v>
       </c>
-      <c r="L14" s="7" t="b">
+      <c r="L14" s="6" t="b">
         <f t="shared" ref="L14:L20" si="3">IF($C$8=1,AND(MAX($K14,$U14,$AE14,$AO14,$AY14)=K14,K14&lt;&gt;0),AND(MAX($K$14:$K$20,$U$14:$U$20,$AE$14:$AE$20,$AO$14:$AO$20,$AY$14:$AY$20)=K14,K14&lt;&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="M14" s="5">
+      <c r="M14" s="4">
         <f>IF(SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12))=0,"-",SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12)))</f>
         <v>0.5</v>
       </c>
-      <c r="N14" s="6" t="b">
+      <c r="N14" s="5" t="b">
         <f t="shared" ref="N14:N20" si="4">IF($C$8=1,AND(MAX($C14,$M14,$W14,$AG14,$AQ14)=M14,M14&lt;&gt;0),AND(MAX($C$14:$C$20,$M$14:$M$20,$W$14:$W$20,$AG$14:$AG$20,$AQ$14:$AQ$20)=M14,M14&lt;&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="O14" s="6">
+      <c r="O14" s="5">
         <f>IF(SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12))=0,"-",SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12)))</f>
         <v>0.48779788288100001</v>
       </c>
-      <c r="P14" s="6" t="b">
+      <c r="P14" s="5" t="b">
         <f t="shared" ref="P14:P20" si="5">IF($C$8=1,AND(MAX($E14,$O14,$Y14,$AI14,$AS14)=O14,O14&lt;&gt;0),AND(MAX($E$14:$E$20,$O$14:$O$20,$Y$14:$Y$20,$AI$14:$AI$20,$AS$14:$AS$14)=O14,O14&lt;&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="Q14" s="6">
+      <c r="Q14" s="5">
         <f>IF(SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12))=0,"-",SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12)))</f>
         <v>0.486853932584</v>
       </c>
-      <c r="R14" s="6" t="b">
+      <c r="R14" s="5" t="b">
         <f t="shared" ref="R14:R20" si="6">IF($C$8=1,AND(MAX($G14,$Q14,$AA14,$AK14,$AU14)=Q14,Q14&lt;&gt;0),AND(MAX($G$14:$G$20,$Q$14:$Q$20,$AA$14:$AA$20,$AK$14:$AK$20,$AU$14:$AU$20)=Q14,Q14&lt;&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="S14" s="6">
+      <c r="S14" s="5">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12)))</f>
         <v>0.48779788288100001</v>
       </c>
-      <c r="T14" s="6" t="b">
+      <c r="T14" s="5" t="b">
         <f t="shared" ref="T14:T20" si="7">IF($C$8=1,AND(MAX($I14,$S14,$AC14,$AM14,$AW14)=S14,S14&lt;&gt;0),AND(MAX($I$14:$I$20,$S$14:$S$20,$AC$14:$AC$20,$AM$14:$AM$20,$AW$14:$AW$20)=S14,S14&lt;&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="U14" s="6">
+      <c r="U14" s="5">
         <f>IF(SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12))=0,"-",SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12)))</f>
         <v>0.48258639851099999</v>
       </c>
-      <c r="V14" s="7" t="b">
+      <c r="V14" s="6" t="b">
         <f t="shared" ref="V14:V20" si="8">IF($C$8=1,AND(MAX($K14,$U14,$AE14,$AO14,$AY14)=U14,U14&lt;&gt;0),AND(MAX($K$14:$K$20,$U$14:$U$20,$AE$14:$AE$20,$AO$14:$AO$20,$AY$14:$AY$20)=U14,U14&lt;&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="W14" s="5">
+      <c r="W14" s="4">
         <f>IF(SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12))=0,"-",SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12)))</f>
         <v>0.48920863309399998</v>
       </c>
-      <c r="X14" s="6" t="b">
+      <c r="X14" s="5" t="b">
         <f t="shared" ref="X14:X20" si="9">IF($C$8=1,AND(MAX($C14,$M14,$W14,$AG14,$AQ14)=W14,W14&lt;&gt;0),AND(MAX($C$14:$C$20,$M$14:$M$20,$W$14:$W$20,$AG$14:$AG$20,$AQ$14:$AQ$20)=W14,W14&lt;&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="Y14" s="6">
+      <c r="Y14" s="5">
         <f>IF(SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12))=0,"-",SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12)))</f>
         <v>0.48287010481300002</v>
       </c>
-      <c r="Z14" s="6" t="b">
+      <c r="Z14" s="5" t="b">
         <f t="shared" ref="Z14:Z20" si="10">IF($C$8=1,AND(MAX($E14,$O14,$Y14,$AI14,$AS14)=Y14,Y14&lt;&gt;0),AND(MAX($E$14:$E$20,$O$14:$O$20,$Y$14:$Y$20,$AI$14:$AI$20,$AS$14:$AS$14)=Y14,Y14&lt;&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="AA14" s="6">
+      <c r="AA14" s="5">
         <f>IF(SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12))=0,"-",SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12)))</f>
         <v>0.482638338354</v>
       </c>
-      <c r="AB14" s="6" t="b">
+      <c r="AB14" s="5" t="b">
         <f t="shared" ref="AB14:AB20" si="11">IF($C$8=1,AND(MAX($G14,$Q14,$AA14,$AK14,$AU14)=AA14,AA14&lt;&gt;0),AND(MAX($G$14:$G$20,$Q$14:$Q$20,$AA$14:$AA$20,$AK$14:$AK$20,$AU$14:$AU$20)=AA14,AA14&lt;&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="AC14" s="6">
+      <c r="AC14" s="5">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12)))</f>
         <v>0.48287010481300002</v>
       </c>
-      <c r="AD14" s="6" t="b">
+      <c r="AD14" s="5" t="b">
         <f t="shared" ref="AD14:AD20" si="12">IF($C$8=1,AND(MAX($I14,$S14,$AC14,$AM14,$AW14)=AC14,AC14&lt;&gt;0),AND(MAX($I$14:$I$20,$S$14:$S$20,$AC$14:$AC$20,$AM$14:$AM$20,$AW$14:$AW$20)=AC14,AC14&lt;&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="AE14" s="6">
+      <c r="AE14" s="5">
         <f>IF(SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12))=0,"-",SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12)))</f>
         <v>0.48234985575700001</v>
       </c>
-      <c r="AF14" s="7" t="b">
+      <c r="AF14" s="6" t="b">
         <f t="shared" ref="AF14:AF20" si="13">IF($C$8=1,AND(MAX($K14,$U14,$AE14,$AO14,$AY14)=AE14,AE14&lt;&gt;0),AND(MAX($K$14:$K$20,$U$14:$U$20,$AE$14:$AE$20,$AO$14:$AO$20,$AY$14:$AY$20)=AE14,AE14&lt;&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="AG14" s="5">
+      <c r="AG14" s="4">
         <f>IF(SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12))=0,"-",SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12)))</f>
         <v>0.5</v>
       </c>
-      <c r="AH14" s="6" t="b">
+      <c r="AH14" s="5" t="b">
         <f t="shared" ref="AH14:AH20" si="14">IF($C$8=1,AND(MAX($C14,$M14,$W14,$AG14,$AQ14)=AG14,AG14&lt;&gt;0),AND(MAX($C$14:$C$20,$M$14:$M$20,$W$14:$W$20,$AG$14:$AG$20,$AQ$14:$AQ$20)=AG14,AG14&lt;&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="AI14" s="6">
+      <c r="AI14" s="5">
         <f>IF(SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12))=0,"-",SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12)))</f>
         <v>0.48717213328499998</v>
       </c>
-      <c r="AJ14" s="6" t="b">
+      <c r="AJ14" s="5" t="b">
         <f t="shared" ref="AJ14:AJ20" si="15">IF($C$8=1,AND(MAX($E14,$O14,$Y14,$AI14,$AS14)=AI14,AI14&lt;&gt;0),AND(MAX($E$14:$E$20,$O$14:$O$20,$Y$14:$Y$20,$AI$14:$AI$20,$AS$14:$AS$14)=AI14,AI14&lt;&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="AK14" s="6">
+      <c r="AK14" s="5">
         <f>IF(SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12))=0,"-",SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12)))</f>
         <v>0.48605442176899999</v>
       </c>
-      <c r="AL14" s="6" t="b">
+      <c r="AL14" s="5" t="b">
         <f t="shared" ref="AL14:AL20" si="16">IF($C$8=1,AND(MAX($G14,$Q14,$AA14,$AK14,$AU14)=AK14,AK14&lt;&gt;0),AND(MAX($G$14:$G$20,$Q$14:$Q$20,$AA$14:$AA$20,$AK$14:$AK$20,$AU$14:$AU$20)=AK14,AK14&lt;&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="AM14" s="6">
+      <c r="AM14" s="5">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12)))</f>
         <v>0.48717213328499998</v>
       </c>
-      <c r="AN14" s="6" t="b">
+      <c r="AN14" s="5" t="b">
         <f t="shared" ref="AN14:AN20" si="17">IF($C$8=1,AND(MAX($I14,$S14,$AC14,$AM14,$AW14)=AM14,AM14&lt;&gt;0),AND(MAX($I$14:$I$20,$S$14:$S$20,$AC$14:$AC$20,$AM$14:$AM$20,$AW$14:$AW$20)=AM14,AM14&lt;&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="AO14" s="6">
+      <c r="AO14" s="5">
         <f>IF(SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12))=0,"-",SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12)))</f>
         <v>0.48114132259100001</v>
       </c>
-      <c r="AP14" s="7" t="b">
+      <c r="AP14" s="6" t="b">
         <f t="shared" ref="AP14:AP20" si="18">IF($C$8=1,AND(MAX($K14,$U14,$AE14,$AO14,$AY14)=AO14,AO14&lt;&gt;0),AND(MAX($K$14:$K$20,$U$14:$U$20,$AE$14:$AE$20,$AO$14:$AO$20,$AY$14:$AY$20)=AO14,AO14&lt;&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="AQ14" s="5">
+      <c r="AQ14" s="4">
         <f>IF(SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12))=0,"-",SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12)))</f>
         <v>0.48920863309399998</v>
       </c>
-      <c r="AR14" s="6" t="b">
+      <c r="AR14" s="5" t="b">
         <f t="shared" ref="AR14:AR20" si="19">IF($C$8=1,AND(MAX($C14,$M14,$W14,$AG14,$AQ14)=AQ14,AQ14&lt;&gt;0),AND(MAX($C$14:$C$20,$M$14:$M$20,$W$14:$W$20,$AG$14:$AG$20,$AQ$14:$AQ$20)=AQ14,AQ14&lt;&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="AS14" s="6">
+      <c r="AS14" s="5">
         <f>IF(SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12))=0,"-",SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12)))</f>
         <v>0.48099285602500003</v>
       </c>
-      <c r="AT14" s="6" t="b">
+      <c r="AT14" s="5" t="b">
         <f t="shared" ref="AT14:AT20" si="20">IF($C$8=1,AND(MAX($E14,$O14,$Y14,$AI14,$AS14)=AS14,AS14&lt;&gt;0),AND(MAX($E$14:$E$20,$O$14:$O$20,$Y$14:$Y$20,$AI$14:$AI$20,$AS$14:$AS$14)=AS14,AS14&lt;&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="AU14" s="6">
+      <c r="AU14" s="5">
         <f>IF(SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12))=0,"-",SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12)))</f>
         <v>0.480450522928</v>
       </c>
-      <c r="AV14" s="6" t="b">
+      <c r="AV14" s="5" t="b">
         <f t="shared" ref="AV14:AV20" si="21">IF($C$8=1,AND(MAX($G14,$Q14,$AA14,$AK14,$AU14)=AU14,AU14&lt;&gt;0),AND(MAX($G$14:$G$20,$Q$14:$Q$20,$AA$14:$AA$20,$AK$14:$AK$20,$AU$14:$AU$20)=AU14,AU14&lt;&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="AW14" s="6">
+      <c r="AW14" s="5">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12)))</f>
         <v>0.48099285602500003</v>
       </c>
-      <c r="AX14" s="6" t="b">
+      <c r="AX14" s="5" t="b">
         <f t="shared" ref="AX14:AX20" si="22">IF($C$8=1,AND(MAX($I14,$S14,$AC14,$AM14,$AW14)=AW14,AW14&lt;&gt;0),AND(MAX($I$14:$I$20,$S$14:$S$20,$AC$14:$AC$20,$AM$14:$AM$20,$AW$14:$AW$20)=AW14,AW14&lt;&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="AY14" s="6">
+      <c r="AY14" s="5">
         <f>IF(SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12))=0,"-",SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B14),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12)))</f>
         <v>0.479483122363</v>
       </c>
-      <c r="AZ14" s="7" t="b">
+      <c r="AZ14" s="6" t="b">
         <f t="shared" ref="AZ14:AZ20" si="23">IF($C$8=1,AND(MAX($K14,$U14,$AE14,$AO14,$AY14)=AY14,AY14&lt;&gt;0),AND(MAX($K$14:$K$20,$U$14:$U$20,$AE$14:$AE$20,$AO$14:$AO$20,$AY$14:$AY$20)=AY14,AY14&lt;&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BA14" s="4"/>
-      <c r="BB14" s="4"/>
+      <c r="BA14" s="3"/>
+      <c r="BB14" s="3"/>
     </row>
-    <row r="15" spans="2:87" x14ac:dyDescent="0.25">
-      <c r="B15" s="18" t="s">
+    <row r="15" spans="2:87" x14ac:dyDescent="0.3">
+      <c r="B15" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="4">
         <f>IF(SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12))=0,"-",SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12)))</f>
         <v>0.471223021583</v>
       </c>
-      <c r="D15" s="6" t="b">
+      <c r="D15" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="5">
         <f>IF(SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12))=0,"-",SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12)))</f>
         <v>0.462559315847</v>
       </c>
-      <c r="F15" s="6" t="b">
+      <c r="F15" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="5">
         <f>IF(SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12))=0,"-",SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12)))</f>
         <v>0.46138123924300001</v>
       </c>
-      <c r="H15" s="6" t="b">
+      <c r="H15" s="5" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I15" s="6">
+      <c r="I15" s="5">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12)))</f>
         <v>0.462559315847</v>
       </c>
-      <c r="J15" s="6" t="b">
+      <c r="J15" s="5" t="b">
         <f t="shared" ref="J15:J20" si="24">IF($C$8=1,AND(MAX($I15,$S15,$AC15,$AM15,$AW15)=I15,I15&lt;&gt;0),AND(MAX($I$14:$I$20,$S$14:$S$20,$AC$14:$AC$20,$AM$14:$AM$20,$AW$14:$AW$20)=I15,I15&lt;&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="5">
         <f>IF(SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12))=0,"-",SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12)))</f>
         <v>0.460607420509</v>
       </c>
-      <c r="L15" s="7" t="b">
+      <c r="L15" s="6" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M15" s="5">
+      <c r="M15" s="4">
         <f>IF(SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12))=0,"-",SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12)))</f>
         <v>0.528776978417</v>
       </c>
-      <c r="N15" s="6" t="b">
+      <c r="N15" s="5" t="b">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O15" s="6">
+      <c r="O15" s="5">
         <f>IF(SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12))=0,"-",SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12)))</f>
         <v>0.52367419304399998</v>
       </c>
-      <c r="P15" s="6" t="b">
+      <c r="P15" s="5" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q15" s="6">
+      <c r="Q15" s="5">
         <f>IF(SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12))=0,"-",SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12)))</f>
         <v>0.52385456074000003</v>
       </c>
-      <c r="R15" s="6" t="b">
+      <c r="R15" s="5" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="S15" s="6">
+      <c r="S15" s="5">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12)))</f>
         <v>0.52367419304399998</v>
       </c>
-      <c r="T15" s="6" t="b">
+      <c r="T15" s="5" t="b">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U15" s="6">
+      <c r="U15" s="5">
         <f>IF(SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12))=0,"-",SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12)))</f>
         <v>0.52359274230499997</v>
       </c>
-      <c r="V15" s="7" t="b">
+      <c r="V15" s="6" t="b">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="W15" s="5">
+      <c r="W15" s="4">
         <f>IF(SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12))=0,"-",SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12)))</f>
         <v>0.45683453237400001</v>
       </c>
-      <c r="X15" s="6" t="b">
+      <c r="X15" s="5" t="b">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Y15" s="6">
+      <c r="Y15" s="5">
         <f>IF(SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12))=0,"-",SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12)))</f>
         <v>0.45432027950100001</v>
       </c>
-      <c r="Z15" s="6" t="b">
+      <c r="Z15" s="5" t="b">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AA15" s="6">
+      <c r="AA15" s="5">
         <f>IF(SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12))=0,"-",SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12)))</f>
         <v>0.45454545454500001</v>
       </c>
-      <c r="AB15" s="6" t="b">
+      <c r="AB15" s="5" t="b">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AC15" s="6">
+      <c r="AC15" s="5">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12)))</f>
         <v>0.45432027950100001</v>
       </c>
-      <c r="AD15" s="6" t="b">
+      <c r="AD15" s="5" t="b">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AE15" s="6">
+      <c r="AE15" s="5">
         <f>IF(SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12))=0,"-",SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12)))</f>
         <v>0.454285454285</v>
       </c>
-      <c r="AF15" s="7" t="b">
+      <c r="AF15" s="6" t="b">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AG15" s="5">
+      <c r="AG15" s="4">
         <f>IF(SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12))=0,"-",SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12)))</f>
         <v>0.51798561151099998</v>
       </c>
-      <c r="AH15" s="6" t="b">
+      <c r="AH15" s="5" t="b">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AI15" s="6">
+      <c r="AI15" s="5">
         <f>IF(SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12))=0,"-",SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12)))</f>
         <v>0.50936017103800002</v>
       </c>
-      <c r="AJ15" s="6" t="b">
+      <c r="AJ15" s="5" t="b">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AK15" s="6">
+      <c r="AK15" s="5">
         <f>IF(SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12))=0,"-",SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12)))</f>
         <v>0.50968333603100002</v>
       </c>
-      <c r="AL15" s="6" t="b">
+      <c r="AL15" s="5" t="b">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AM15" s="6">
+      <c r="AM15" s="5">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12)))</f>
         <v>0.50936017103800002</v>
       </c>
-      <c r="AN15" s="6" t="b">
+      <c r="AN15" s="5" t="b">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AO15" s="6">
+      <c r="AO15" s="5">
         <f>IF(SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12))=0,"-",SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12)))</f>
         <v>0.50779557105899997</v>
       </c>
-      <c r="AP15" s="7" t="b">
+      <c r="AP15" s="6" t="b">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AQ15" s="5">
+      <c r="AQ15" s="4">
         <f>IF(SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12))=0,"-",SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12)))</f>
         <v>0.460431654676</v>
       </c>
-      <c r="AR15" s="6" t="b">
+      <c r="AR15" s="5" t="b">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AS15" s="6">
+      <c r="AS15" s="5">
         <f>IF(SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12))=0,"-",SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12)))</f>
         <v>0.45575428899199999</v>
       </c>
-      <c r="AT15" s="6" t="b">
+      <c r="AT15" s="5" t="b">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AU15" s="6">
+      <c r="AU15" s="5">
         <f>IF(SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12))=0,"-",SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12)))</f>
         <v>0.455633986928</v>
       </c>
-      <c r="AV15" s="6" t="b">
+      <c r="AV15" s="5" t="b">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="AW15" s="6">
+      <c r="AW15" s="5">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12)))</f>
         <v>0.45575428899199999</v>
       </c>
-      <c r="AX15" s="6" t="b">
+      <c r="AX15" s="5" t="b">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AY15" s="6">
+      <c r="AY15" s="5">
         <f>IF(SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12))=0,"-",SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B15),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12)))</f>
         <v>0.45567042606500002</v>
       </c>
-      <c r="AZ15" s="7" t="b">
+      <c r="AZ15" s="6" t="b">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:87" x14ac:dyDescent="0.25">
-      <c r="B16" s="8" t="s">
+    <row r="16" spans="2:87" x14ac:dyDescent="0.3">
+      <c r="B16" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="4">
         <f>IF(SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12))=0,"-",SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12)))</f>
         <v>0.38489208633100003</v>
       </c>
-      <c r="D16" s="6" t="b">
+      <c r="D16" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="5">
         <f>IF(SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12))=0,"-",SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12)))</f>
         <v>0.38058611878800003</v>
       </c>
-      <c r="F16" s="6" t="b">
+      <c r="F16" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="5">
         <f>IF(SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12))=0,"-",SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12)))</f>
         <v>0.38072916666700002</v>
       </c>
-      <c r="H16" s="6" t="b">
+      <c r="H16" s="5" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I16" s="6">
+      <c r="I16" s="5">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12)))</f>
         <v>0.38058611878800003</v>
       </c>
-      <c r="J16" s="6" t="b">
+      <c r="J16" s="5" t="b">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="K16" s="6">
+      <c r="K16" s="5">
         <f>IF(SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12))=0,"-",SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12)))</f>
         <v>0.38065272620700003</v>
       </c>
-      <c r="L16" s="7" t="b">
+      <c r="L16" s="6" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M16" s="5">
+      <c r="M16" s="4">
         <f>IF(SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12))=0,"-",SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12)))</f>
         <v>0.51798561151099998</v>
       </c>
-      <c r="N16" s="6" t="b">
+      <c r="N16" s="5" t="b">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O16" s="6">
+      <c r="O16" s="5">
         <f>IF(SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12))=0,"-",SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12)))</f>
         <v>0.514366167805</v>
       </c>
-      <c r="P16" s="6" t="b">
+      <c r="P16" s="5" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q16" s="6">
+      <c r="Q16" s="5">
         <f>IF(SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12))=0,"-",SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12)))</f>
         <v>0.514366167805</v>
       </c>
-      <c r="R16" s="6" t="b">
+      <c r="R16" s="5" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="S16" s="6">
+      <c r="S16" s="5">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12)))</f>
         <v>0.514366167805</v>
       </c>
-      <c r="T16" s="6" t="b">
+      <c r="T16" s="5" t="b">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U16" s="6">
+      <c r="U16" s="5">
         <f>IF(SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12))=0,"-",SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12)))</f>
         <v>0.514366167805</v>
       </c>
-      <c r="V16" s="7" t="b">
+      <c r="V16" s="6" t="b">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="W16" s="5">
+      <c r="W16" s="4">
         <f>IF(SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12))=0,"-",SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12)))</f>
         <v>0.40647482014399999</v>
       </c>
-      <c r="X16" s="6" t="b">
+      <c r="X16" s="5" t="b">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Y16" s="6">
+      <c r="Y16" s="5">
         <f>IF(SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12))=0,"-",SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12)))</f>
         <v>0.40045366845699998</v>
       </c>
-      <c r="Z16" s="6" t="b">
+      <c r="Z16" s="5" t="b">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AA16" s="6">
+      <c r="AA16" s="5">
         <f>IF(SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12))=0,"-",SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12)))</f>
         <v>0.39969525010500001</v>
       </c>
-      <c r="AB16" s="6" t="b">
+      <c r="AB16" s="5" t="b">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AC16" s="6">
+      <c r="AC16" s="5">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12)))</f>
         <v>0.40045366845699998</v>
       </c>
-      <c r="AD16" s="6" t="b">
+      <c r="AD16" s="5" t="b">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AE16" s="6">
+      <c r="AE16" s="5">
         <f>IF(SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12))=0,"-",SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12)))</f>
         <v>0.39994505710099998</v>
       </c>
-      <c r="AF16" s="7" t="b">
+      <c r="AF16" s="6" t="b">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AG16" s="5">
+      <c r="AG16" s="4">
         <f>IF(SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12))=0,"-",SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12)))</f>
         <v>0.41726618705000001</v>
       </c>
-      <c r="AH16" s="6" t="b">
+      <c r="AH16" s="5" t="b">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AI16" s="6">
+      <c r="AI16" s="5">
         <f>IF(SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12))=0,"-",SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12)))</f>
         <v>0.40913594409999998</v>
       </c>
-      <c r="AJ16" s="6" t="b">
+      <c r="AJ16" s="5" t="b">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AK16" s="6">
+      <c r="AK16" s="5">
         <f>IF(SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12))=0,"-",SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12)))</f>
         <v>0.40704187783399998</v>
       </c>
-      <c r="AL16" s="6" t="b">
+      <c r="AL16" s="5" t="b">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AM16" s="6">
+      <c r="AM16" s="5">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12)))</f>
         <v>0.40913594409999998</v>
       </c>
-      <c r="AN16" s="6" t="b">
+      <c r="AN16" s="5" t="b">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AO16" s="6">
+      <c r="AO16" s="5">
         <f>IF(SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12))=0,"-",SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12)))</f>
         <v>0.407327472759</v>
       </c>
-      <c r="AP16" s="7" t="b">
+      <c r="AP16" s="6" t="b">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AQ16" s="5">
+      <c r="AQ16" s="4">
         <f>IF(SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12))=0,"-",SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12)))</f>
         <v>0.28776978417299998</v>
       </c>
-      <c r="AR16" s="6" t="b">
+      <c r="AR16" s="5" t="b">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AS16" s="6">
+      <c r="AS16" s="5">
         <f>IF(SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12))=0,"-",SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12)))</f>
         <v>0.29055639568199998</v>
       </c>
-      <c r="AT16" s="6" t="b">
+      <c r="AT16" s="5" t="b">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AU16" s="6">
+      <c r="AU16" s="5">
         <f>IF(SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12))=0,"-",SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12)))</f>
         <v>0.28998692810499999</v>
       </c>
-      <c r="AV16" s="6" t="b">
+      <c r="AV16" s="5" t="b">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="AW16" s="6">
+      <c r="AW16" s="5">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12)))</f>
         <v>0.29055639568199998</v>
       </c>
-      <c r="AX16" s="6" t="b">
+      <c r="AX16" s="5" t="b">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AY16" s="6">
+      <c r="AY16" s="5">
         <f>IF(SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12))=0,"-",SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B16),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12)))</f>
         <v>0.287732919255</v>
       </c>
-      <c r="AZ16" s="7" t="b">
+      <c r="AZ16" s="6" t="b">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B17" s="18" t="s">
+    <row r="17" spans="2:52" x14ac:dyDescent="0.3">
+      <c r="B17" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="4">
         <f>IF(SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12))=0,"-",SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12)))</f>
         <v>0.53597122302199995</v>
       </c>
-      <c r="D17" s="6" t="b">
+      <c r="D17" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="5">
         <f>IF(SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12))=0,"-",SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12)))</f>
         <v>0.53092245919600001</v>
       </c>
-      <c r="F17" s="6" t="b">
+      <c r="F17" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17" s="5">
         <f>IF(SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12))=0,"-",SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12)))</f>
         <v>0.53115804960099999</v>
       </c>
-      <c r="H17" s="6" t="b">
+      <c r="H17" s="5" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I17" s="6">
+      <c r="I17" s="5">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12)))</f>
         <v>0.53092245919600001</v>
       </c>
-      <c r="J17" s="6" t="b">
+      <c r="J17" s="5" t="b">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="K17" s="6">
+      <c r="K17" s="5">
         <f>IF(SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12))=0,"-",SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12)))</f>
         <v>0.53086613555200002</v>
       </c>
-      <c r="L17" s="7" t="b">
+      <c r="L17" s="6" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M17" s="5">
+      <c r="M17" s="4">
         <f>IF(SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12))=0,"-",SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12)))</f>
         <v>0.49280575539600002</v>
       </c>
-      <c r="N17" s="6" t="b">
+      <c r="N17" s="5" t="b">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O17" s="6">
+      <c r="O17" s="5">
         <f>IF(SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12))=0,"-",SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12)))</f>
         <v>0.484929863899</v>
       </c>
-      <c r="P17" s="6" t="b">
+      <c r="P17" s="5" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q17" s="6">
+      <c r="Q17" s="5">
         <f>IF(SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12))=0,"-",SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12)))</f>
         <v>0.484542148053</v>
       </c>
-      <c r="R17" s="6" t="b">
+      <c r="R17" s="5" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="S17" s="6">
+      <c r="S17" s="5">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12)))</f>
         <v>0.484929863899</v>
       </c>
-      <c r="T17" s="6" t="b">
+      <c r="T17" s="5" t="b">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U17" s="6">
+      <c r="U17" s="5">
         <f>IF(SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12))=0,"-",SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12)))</f>
         <v>0.483659355859</v>
       </c>
-      <c r="V17" s="7" t="b">
+      <c r="V17" s="6" t="b">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="W17" s="5">
+      <c r="W17" s="4">
         <f>IF(SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12))=0,"-",SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12)))</f>
         <v>0.49640287769800001</v>
       </c>
-      <c r="X17" s="6" t="b">
+      <c r="X17" s="5" t="b">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Y17" s="6">
+      <c r="Y17" s="5">
         <f>IF(SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12))=0,"-",SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12)))</f>
         <v>0.49262136934900003</v>
       </c>
-      <c r="Z17" s="6" t="b">
+      <c r="Z17" s="5" t="b">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AA17" s="6">
+      <c r="AA17" s="5">
         <f>IF(SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12))=0,"-",SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12)))</f>
         <v>0.49262136934900003</v>
       </c>
-      <c r="AB17" s="6" t="b">
+      <c r="AB17" s="5" t="b">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AC17" s="6">
+      <c r="AC17" s="5">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12)))</f>
         <v>0.49262136934900003</v>
       </c>
-      <c r="AD17" s="6" t="b">
+      <c r="AD17" s="5" t="b">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AE17" s="6">
+      <c r="AE17" s="5">
         <f>IF(SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12))=0,"-",SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12)))</f>
         <v>0.49262136934900003</v>
       </c>
-      <c r="AF17" s="7" t="b">
+      <c r="AF17" s="6" t="b">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AG17" s="5">
+      <c r="AG17" s="4">
         <f>IF(SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12))=0,"-",SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12)))</f>
         <v>0.48561151079100001</v>
       </c>
-      <c r="AH17" s="6" t="b">
+      <c r="AH17" s="5" t="b">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AI17" s="6">
+      <c r="AI17" s="5">
         <f>IF(SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12))=0,"-",SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12)))</f>
         <v>0.47705584815099999</v>
       </c>
-      <c r="AJ17" s="6" t="b">
+      <c r="AJ17" s="5" t="b">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AK17" s="6">
+      <c r="AK17" s="5">
         <f>IF(SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12))=0,"-",SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12)))</f>
         <v>0.47633390705700002</v>
       </c>
-      <c r="AL17" s="6" t="b">
+      <c r="AL17" s="5" t="b">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AM17" s="6">
+      <c r="AM17" s="5">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12)))</f>
         <v>0.47705584815099999</v>
       </c>
-      <c r="AN17" s="6" t="b">
+      <c r="AN17" s="5" t="b">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AO17" s="6">
+      <c r="AO17" s="5">
         <f>IF(SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12))=0,"-",SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12)))</f>
         <v>0.47528476960999999</v>
       </c>
-      <c r="AP17" s="7" t="b">
+      <c r="AP17" s="6" t="b">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AQ17" s="5">
+      <c r="AQ17" s="4">
         <f>IF(SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12))=0,"-",SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12)))</f>
         <v>0.471223021583</v>
       </c>
-      <c r="AR17" s="6" t="b">
+      <c r="AR17" s="5" t="b">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AS17" s="6">
+      <c r="AS17" s="5">
         <f>IF(SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12))=0,"-",SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12)))</f>
         <v>0.46568806382599998</v>
       </c>
-      <c r="AT17" s="6" t="b">
+      <c r="AT17" s="5" t="b">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AU17" s="6">
+      <c r="AU17" s="5">
         <f>IF(SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12))=0,"-",SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12)))</f>
         <v>0.46542664985299997</v>
       </c>
-      <c r="AV17" s="6" t="b">
+      <c r="AV17" s="5" t="b">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="AW17" s="6">
+      <c r="AW17" s="5">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12)))</f>
         <v>0.46568806382599998</v>
       </c>
-      <c r="AX17" s="6" t="b">
+      <c r="AX17" s="5" t="b">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AY17" s="6">
+      <c r="AY17" s="5">
         <f>IF(SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12))=0,"-",SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B17),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12)))</f>
         <v>0.46540559632700002</v>
       </c>
-      <c r="AZ17" s="7" t="b">
+      <c r="AZ17" s="6" t="b">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B18" s="8" t="s">
+    <row r="18" spans="2:52" x14ac:dyDescent="0.3">
+      <c r="B18" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="4">
         <f>IF(SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12))=0,"-",SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12)))</f>
         <v>0.50719424460399998</v>
       </c>
-      <c r="D18" s="6" t="b">
+      <c r="D18" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="5">
         <f>IF(SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12))=0,"-",SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12)))</f>
         <v>0.50380664337500003</v>
       </c>
-      <c r="F18" s="6" t="b">
+      <c r="F18" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18" s="5">
         <f>IF(SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12))=0,"-",SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12)))</f>
         <v>0.50380208333300003</v>
       </c>
-      <c r="H18" s="6" t="b">
+      <c r="H18" s="5" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I18" s="6">
+      <c r="I18" s="5">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12)))</f>
         <v>0.50380664337500003</v>
       </c>
-      <c r="J18" s="6" t="b">
+      <c r="J18" s="5" t="b">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="K18" s="6">
+      <c r="K18" s="5">
         <f>IF(SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12))=0,"-",SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12)))</f>
         <v>0.50379779818899995</v>
       </c>
-      <c r="L18" s="7" t="b">
+      <c r="L18" s="6" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M18" s="5">
+      <c r="M18" s="4">
         <f>IF(SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12))=0,"-",SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12)))</f>
         <v>0.55755395683499998</v>
       </c>
-      <c r="N18" s="6" t="b">
+      <c r="N18" s="5" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="O18" s="6">
+      <c r="O18" s="5">
         <f>IF(SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12))=0,"-",SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12)))</f>
         <v>0.55079000886499996</v>
       </c>
-      <c r="P18" s="6" t="b">
+      <c r="P18" s="5" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q18" s="6">
+      <c r="Q18" s="5">
         <f>IF(SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12))=0,"-",SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12)))</f>
         <v>0.55183056619799997</v>
       </c>
-      <c r="R18" s="6" t="b">
+      <c r="R18" s="5" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="S18" s="6">
+      <c r="S18" s="5">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12)))</f>
         <v>0.55079000886499996</v>
       </c>
-      <c r="T18" s="6" t="b">
+      <c r="T18" s="5" t="b">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U18" s="6">
+      <c r="U18" s="5">
         <f>IF(SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12))=0,"-",SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12)))</f>
         <v>0.55042795724399995</v>
       </c>
-      <c r="V18" s="7" t="b">
+      <c r="V18" s="6" t="b">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="W18" s="5">
+      <c r="W18" s="4">
         <f>IF(SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12))=0,"-",SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12)))</f>
         <v>0.55755395683499998</v>
       </c>
-      <c r="X18" s="6" t="b">
+      <c r="X18" s="5" t="b">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="Y18" s="6">
+      <c r="Y18" s="5">
         <f>IF(SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12))=0,"-",SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12)))</f>
         <v>0.55204150805700003</v>
       </c>
-      <c r="Z18" s="6" t="b">
+      <c r="Z18" s="5" t="b">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="AA18" s="6">
+      <c r="AA18" s="5">
         <f>IF(SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12))=0,"-",SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12)))</f>
         <v>0.55263713080200005</v>
       </c>
-      <c r="AB18" s="6" t="b">
+      <c r="AB18" s="5" t="b">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="AC18" s="6">
+      <c r="AC18" s="5">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12)))</f>
         <v>0.55204150805700003</v>
       </c>
-      <c r="AD18" s="6" t="b">
+      <c r="AD18" s="5" t="b">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="AE18" s="6">
+      <c r="AE18" s="5">
         <f>IF(SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12))=0,"-",SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12)))</f>
         <v>0.55198301953499995</v>
       </c>
-      <c r="AF18" s="7" t="b">
+      <c r="AF18" s="6" t="b">
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
-      <c r="AG18" s="5">
+      <c r="AG18" s="4">
         <f>IF(SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12))=0,"-",SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12)))</f>
         <v>0.539568345324</v>
       </c>
-      <c r="AH18" s="6" t="b">
+      <c r="AH18" s="5" t="b">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AI18" s="6">
+      <c r="AI18" s="5">
         <f>IF(SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12))=0,"-",SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12)))</f>
         <v>0.53611096626200005</v>
       </c>
-      <c r="AJ18" s="6" t="b">
+      <c r="AJ18" s="5" t="b">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AK18" s="6">
+      <c r="AK18" s="5">
         <f>IF(SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12))=0,"-",SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12)))</f>
         <v>0.53611096626200005</v>
       </c>
-      <c r="AL18" s="6" t="b">
+      <c r="AL18" s="5" t="b">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AM18" s="6">
+      <c r="AM18" s="5">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12)))</f>
         <v>0.53611096626200005</v>
       </c>
-      <c r="AN18" s="6" t="b">
+      <c r="AN18" s="5" t="b">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AO18" s="6">
+      <c r="AO18" s="5">
         <f>IF(SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12))=0,"-",SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12)))</f>
         <v>0.53611096626200005</v>
       </c>
-      <c r="AP18" s="7" t="b">
+      <c r="AP18" s="6" t="b">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AQ18" s="5">
+      <c r="AQ18" s="4">
         <f>IF(SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12))=0,"-",SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12)))</f>
         <v>0.48201438848900002</v>
       </c>
-      <c r="AR18" s="6" t="b">
+      <c r="AR18" s="5" t="b">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AS18" s="6">
+      <c r="AS18" s="5">
         <f>IF(SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12))=0,"-",SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12)))</f>
         <v>0.48688533138700002</v>
       </c>
-      <c r="AT18" s="6" t="b">
+      <c r="AT18" s="5" t="b">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AU18" s="6">
+      <c r="AU18" s="5">
         <f>IF(SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12))=0,"-",SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12)))</f>
         <v>0.48680828743799998</v>
       </c>
-      <c r="AV18" s="6" t="b">
+      <c r="AV18" s="5" t="b">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="AW18" s="6">
+      <c r="AW18" s="5">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12)))</f>
         <v>0.48688533138700002</v>
       </c>
-      <c r="AX18" s="6" t="b">
+      <c r="AX18" s="5" t="b">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AY18" s="6">
+      <c r="AY18" s="5">
         <f>IF(SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12))=0,"-",SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B18),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12)))</f>
         <v>0.48190712843599998</v>
       </c>
-      <c r="AZ18" s="7" t="b">
+      <c r="AZ18" s="6" t="b">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B19" s="18" t="s">
+    <row r="19" spans="2:52" x14ac:dyDescent="0.3">
+      <c r="B19" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="C19" s="5" t="str">
+      <c r="C19" s="4" t="str">
         <f>IF(SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12))=0,"-",SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12)))</f>
         <v>-</v>
       </c>
-      <c r="D19" s="6" t="b">
+      <c r="D19" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E19" s="6" t="str">
+      <c r="E19" s="5" t="str">
         <f>IF(SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12))=0,"-",SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12)))</f>
         <v>-</v>
       </c>
-      <c r="F19" s="6" t="b">
+      <c r="F19" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G19" s="6" t="str">
+      <c r="G19" s="5" t="str">
         <f>IF(SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12))=0,"-",SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12)))</f>
         <v>-</v>
       </c>
-      <c r="H19" s="6" t="b">
+      <c r="H19" s="5" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I19" s="6" t="str">
+      <c r="I19" s="5" t="str">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12)))</f>
         <v>-</v>
       </c>
-      <c r="J19" s="6" t="b">
+      <c r="J19" s="5" t="b">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="K19" s="6" t="str">
+      <c r="K19" s="5" t="str">
         <f>IF(SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12))=0,"-",SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12)))</f>
         <v>-</v>
       </c>
-      <c r="L19" s="7" t="b">
+      <c r="L19" s="6" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M19" s="5">
+      <c r="M19" s="4">
         <f>IF(SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12))=0,"-",SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12)))</f>
         <v>0.47482014388499999</v>
       </c>
-      <c r="N19" s="6" t="b">
+      <c r="N19" s="5" t="b">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O19" s="6">
+      <c r="O19" s="5">
         <f>IF(SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12))=0,"-",SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12)))</f>
         <v>0.471502320488</v>
       </c>
-      <c r="P19" s="6" t="b">
+      <c r="P19" s="5" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q19" s="6">
+      <c r="Q19" s="5">
         <f>IF(SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12))=0,"-",SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12)))</f>
         <v>0.47156755631899999</v>
       </c>
-      <c r="R19" s="6" t="b">
+      <c r="R19" s="5" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="S19" s="6">
+      <c r="S19" s="5">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12)))</f>
         <v>0.471502320488</v>
       </c>
-      <c r="T19" s="6" t="b">
+      <c r="T19" s="5" t="b">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U19" s="6">
+      <c r="U19" s="5">
         <f>IF(SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12))=0,"-",SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12)))</f>
         <v>0.471510416667</v>
       </c>
-      <c r="V19" s="7" t="b">
+      <c r="V19" s="6" t="b">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="W19" s="5">
+      <c r="W19" s="4">
         <f>IF(SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12))=0,"-",SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12)))</f>
         <v>0.43884892086299998</v>
       </c>
-      <c r="X19" s="6" t="b">
+      <c r="X19" s="5" t="b">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Y19" s="6">
+      <c r="Y19" s="5">
         <f>IF(SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12))=0,"-",SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12)))</f>
         <v>0.43400949053600002</v>
       </c>
-      <c r="Z19" s="6" t="b">
+      <c r="Z19" s="5" t="b">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AA19" s="6">
+      <c r="AA19" s="5">
         <f>IF(SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12))=0,"-",SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12)))</f>
         <v>0.43383006535899998</v>
       </c>
-      <c r="AB19" s="6" t="b">
+      <c r="AB19" s="5" t="b">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AC19" s="6">
+      <c r="AC19" s="5">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12)))</f>
         <v>0.43400949053600002</v>
       </c>
-      <c r="AD19" s="6" t="b">
+      <c r="AD19" s="5" t="b">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AE19" s="6">
+      <c r="AE19" s="5">
         <f>IF(SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12))=0,"-",SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12)))</f>
         <v>0.43389724310799999</v>
       </c>
-      <c r="AF19" s="7" t="b">
+      <c r="AF19" s="6" t="b">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AG19" s="5" t="str">
+      <c r="AG19" s="4" t="str">
         <f>IF(SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12))=0,"-",SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12)))</f>
         <v>-</v>
       </c>
-      <c r="AH19" s="6" t="b">
+      <c r="AH19" s="5" t="b">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AI19" s="6" t="str">
+      <c r="AI19" s="5" t="str">
         <f>IF(SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12))=0,"-",SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12)))</f>
         <v>-</v>
       </c>
-      <c r="AJ19" s="6" t="b">
+      <c r="AJ19" s="5" t="b">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AK19" s="6" t="str">
+      <c r="AK19" s="5" t="str">
         <f>IF(SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12))=0,"-",SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12)))</f>
         <v>-</v>
       </c>
-      <c r="AL19" s="6" t="b">
+      <c r="AL19" s="5" t="b">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AM19" s="6" t="str">
+      <c r="AM19" s="5" t="str">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12)))</f>
         <v>-</v>
       </c>
-      <c r="AN19" s="6" t="b">
+      <c r="AN19" s="5" t="b">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AO19" s="6" t="str">
+      <c r="AO19" s="5" t="str">
         <f>IF(SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12))=0,"-",SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12)))</f>
         <v>-</v>
       </c>
-      <c r="AP19" s="7" t="b">
+      <c r="AP19" s="6" t="b">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AQ19" s="5" t="str">
+      <c r="AQ19" s="4" t="str">
         <f>IF(SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12))=0,"-",SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12)))</f>
         <v>-</v>
       </c>
-      <c r="AR19" s="6" t="b">
+      <c r="AR19" s="5" t="b">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AS19" s="6" t="str">
+      <c r="AS19" s="5" t="str">
         <f>IF(SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12))=0,"-",SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12)))</f>
         <v>-</v>
       </c>
-      <c r="AT19" s="6" t="b">
+      <c r="AT19" s="5" t="b">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AU19" s="6" t="str">
+      <c r="AU19" s="5" t="str">
         <f>IF(SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12))=0,"-",SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12)))</f>
         <v>-</v>
       </c>
-      <c r="AV19" s="6" t="b">
+      <c r="AV19" s="5" t="b">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="AW19" s="6" t="str">
+      <c r="AW19" s="5" t="str">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12)))</f>
         <v>-</v>
       </c>
-      <c r="AX19" s="6" t="b">
+      <c r="AX19" s="5" t="b">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AY19" s="6" t="str">
+      <c r="AY19" s="5" t="str">
         <f>IF(SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12))=0,"-",SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B19),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12)))</f>
         <v>-</v>
       </c>
-      <c r="AZ19" s="7" t="b">
+      <c r="AZ19" s="6" t="b">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="9" t="s">
+    <row r="20" spans="2:52" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="C20" s="5" t="str">
+      <c r="C20" s="4" t="str">
         <f>IF(SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12))=0,"-",SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12)))</f>
         <v>-</v>
       </c>
-      <c r="D20" s="6" t="b">
+      <c r="D20" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E20" s="6" t="str">
+      <c r="E20" s="5" t="str">
         <f>IF(SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12))=0,"-",SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12)))</f>
         <v>-</v>
       </c>
-      <c r="F20" s="6" t="b">
+      <c r="F20" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G20" s="6" t="str">
+      <c r="G20" s="5" t="str">
         <f>IF(SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12))=0,"-",SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12)))</f>
         <v>-</v>
       </c>
-      <c r="H20" s="6" t="b">
+      <c r="H20" s="5" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I20" s="6" t="str">
+      <c r="I20" s="5" t="str">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12)))</f>
         <v>-</v>
       </c>
-      <c r="J20" s="6" t="b">
+      <c r="J20" s="5" t="b">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="K20" s="6" t="str">
+      <c r="K20" s="5" t="str">
         <f>IF(SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12))=0,"-",SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(C$12)))</f>
         <v>-</v>
       </c>
-      <c r="L20" s="7" t="b">
+      <c r="L20" s="6" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M20" s="5">
+      <c r="M20" s="4">
         <f>IF(SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12))=0,"-",SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12)))</f>
         <v>0.48561151079100001</v>
       </c>
-      <c r="N20" s="6" t="b">
+      <c r="N20" s="5" t="b">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O20" s="6">
+      <c r="O20" s="5">
         <f>IF(SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12))=0,"-",SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12)))</f>
         <v>0.48331334410999999</v>
       </c>
-      <c r="P20" s="6" t="b">
+      <c r="P20" s="5" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q20" s="6">
+      <c r="Q20" s="5">
         <f>IF(SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12))=0,"-",SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12)))</f>
         <v>0.48339559983399999</v>
       </c>
-      <c r="R20" s="6" t="b">
+      <c r="R20" s="5" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="S20" s="6">
+      <c r="S20" s="5">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12)))</f>
         <v>0.48331334410999999</v>
       </c>
-      <c r="T20" s="6" t="b">
+      <c r="T20" s="5" t="b">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U20" s="6">
+      <c r="U20" s="5">
         <f>IF(SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12))=0,"-",SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(M$12)))</f>
         <v>0.48319748319700001</v>
       </c>
-      <c r="V20" s="7" t="b">
+      <c r="V20" s="6" t="b">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="W20" s="5">
+      <c r="W20" s="4">
         <f>IF(SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12))=0,"-",SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12)))</f>
         <v>0.48920863309399998</v>
       </c>
-      <c r="X20" s="6" t="b">
+      <c r="X20" s="5" t="b">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Y20" s="6">
+      <c r="Y20" s="5">
         <f>IF(SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12))=0,"-",SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12)))</f>
         <v>0.48036710643000002</v>
       </c>
-      <c r="Z20" s="6" t="b">
+      <c r="Z20" s="5" t="b">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AA20" s="6">
+      <c r="AA20" s="5">
         <f>IF(SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12))=0,"-",SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12)))</f>
         <v>0.479689270108</v>
       </c>
-      <c r="AB20" s="6" t="b">
+      <c r="AB20" s="5" t="b">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AC20" s="6">
+      <c r="AC20" s="5">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12)))</f>
         <v>0.48036710643000002</v>
       </c>
-      <c r="AD20" s="6" t="b">
+      <c r="AD20" s="5" t="b">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AE20" s="6">
+      <c r="AE20" s="5">
         <f>IF(SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12))=0,"-",SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(W$12)))</f>
         <v>0.478410232017</v>
       </c>
-      <c r="AF20" s="7" t="b">
+      <c r="AF20" s="6" t="b">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AG20" s="5" t="str">
+      <c r="AG20" s="4" t="str">
         <f>IF(SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12))=0,"-",SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12)))</f>
         <v>-</v>
       </c>
-      <c r="AH20" s="6" t="b">
+      <c r="AH20" s="5" t="b">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AI20" s="6" t="str">
+      <c r="AI20" s="5" t="str">
         <f>IF(SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12))=0,"-",SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12)))</f>
         <v>-</v>
       </c>
-      <c r="AJ20" s="6" t="b">
+      <c r="AJ20" s="5" t="b">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AK20" s="6" t="str">
+      <c r="AK20" s="5" t="str">
         <f>IF(SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12))=0,"-",SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12)))</f>
         <v>-</v>
       </c>
-      <c r="AL20" s="6" t="b">
+      <c r="AL20" s="5" t="b">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AM20" s="6" t="str">
+      <c r="AM20" s="5" t="str">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12)))</f>
         <v>-</v>
       </c>
-      <c r="AN20" s="6" t="b">
+      <c r="AN20" s="5" t="b">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AO20" s="6" t="str">
+      <c r="AO20" s="5" t="str">
         <f>IF(SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12))=0,"-",SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AG$12)))</f>
         <v>-</v>
       </c>
-      <c r="AP20" s="7" t="b">
+      <c r="AP20" s="6" t="b">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="AQ20" s="5" t="str">
+      <c r="AQ20" s="4" t="str">
         <f>IF(SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12))=0,"-",SUMIFS(DATA!$T:$T,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12)))</f>
         <v>-</v>
       </c>
-      <c r="AR20" s="6" t="b">
+      <c r="AR20" s="5" t="b">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="AS20" s="6" t="str">
+      <c r="AS20" s="5" t="str">
         <f>IF(SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12))=0,"-",SUMIFS(DATA!$U:$U,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12)))</f>
         <v>-</v>
       </c>
-      <c r="AT20" s="6" t="b">
+      <c r="AT20" s="5" t="b">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AU20" s="6" t="str">
+      <c r="AU20" s="5" t="str">
         <f>IF(SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12))=0,"-",SUMIFS(DATA!$V:$V,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12)))</f>
         <v>-</v>
       </c>
-      <c r="AV20" s="6" t="b">
+      <c r="AV20" s="5" t="b">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="AW20" s="6" t="str">
+      <c r="AW20" s="5" t="str">
         <f>IF(SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12))=0,"-",SUMIFS(DATA!$W:$W,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12)))</f>
         <v>-</v>
       </c>
-      <c r="AX20" s="6" t="b">
+      <c r="AX20" s="5" t="b">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AY20" s="6" t="str">
+      <c r="AY20" s="5" t="str">
         <f>IF(SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12))=0,"-",SUMIFS(DATA!$X:$X,DATA!$H:$H,LOWER($B20),DATA!$C:$C,_xlfn.NUMBERVALUE(LEFT($D$2,2)),DATA!$D:$D,_xlfn.NUMBERVALUE(MID($D$2,FIND("/",$D$2)+1,LEN($D$2))),DATA!$E:$E,$D$6,DATA!$F:$F,$D$4,DATA!$G:$G,LOWER(AQ$12)))</f>
         <v>-</v>
       </c>
-      <c r="AZ20" s="7" t="b">
+      <c r="AZ20" s="6" t="b">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
@@ -22578,15 +22563,15 @@
                 <anchor>
                   <from>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>1</xdr:row>
-                    <xdr:rowOff>9525</xdr:rowOff>
+                    <xdr:rowOff>7620</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>6</xdr:col>
-                    <xdr:colOff>28575</xdr:colOff>
+                    <xdr:colOff>30480</xdr:colOff>
                     <xdr:row>1</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -22600,15 +22585,15 @@
                 <anchor>
                   <from>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>9525</xdr:colOff>
+                    <xdr:colOff>7620</xdr:colOff>
                     <xdr:row>3</xdr:row>
-                    <xdr:rowOff>9525</xdr:rowOff>
+                    <xdr:rowOff>7620</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>6</xdr:col>
-                    <xdr:colOff>28575</xdr:colOff>
+                    <xdr:colOff>30480</xdr:colOff>
                     <xdr:row>3</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -22622,15 +22607,15 @@
                 <anchor>
                   <from>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>5</xdr:row>
-                    <xdr:rowOff>9525</xdr:rowOff>
+                    <xdr:rowOff>7620</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>6</xdr:col>
                     <xdr:colOff>38100</xdr:colOff>
                     <xdr:row>5</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -22644,15 +22629,15 @@
                 <anchor>
                   <from>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>7</xdr:row>
-                    <xdr:rowOff>9525</xdr:rowOff>
+                    <xdr:rowOff>7620</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>6</xdr:col>
                     <xdr:colOff>38100</xdr:colOff>
                     <xdr:row>7</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -22666,15 +22651,15 @@
                 <anchor>
                   <from>
                     <xdr:col>2</xdr:col>
-                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:colOff>22860</xdr:colOff>
                     <xdr:row>9</xdr:row>
-                    <xdr:rowOff>9525</xdr:rowOff>
+                    <xdr:rowOff>7620</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>6</xdr:col>
                     <xdr:colOff>38100</xdr:colOff>
                     <xdr:row>9</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
+                    <xdr:rowOff>182880</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
